--- a/notebooks/rda-experiments/runs/v11-sample3/evaluation_results.xlsx
+++ b/notebooks/rda-experiments/runs/v11-sample3/evaluation_results.xlsx
@@ -335,7 +335,7 @@
     <t>Software generated under the project</t>
   </si>
   <si>
-    <t>only 50% of the model's words are in the reference</t>
+    <t>only 0% of the model's words are in the reference</t>
   </si>
   <si>
     <t>only 20% of the model's words are in the reference</t>
@@ -2609,7 +2609,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
@@ -2626,7 +2626,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
         <v>28</v>
@@ -2646,7 +2646,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
         <v>29</v>
@@ -2666,7 +2666,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
         <v>30</v>
@@ -2686,7 +2686,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -2695,13 +2695,10 @@
         <v>102</v>
       </c>
       <c r="E11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F11" t="s">
-        <v>89</v>
-      </c>
-      <c r="G11" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2709,7 +2706,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
         <v>32</v>
@@ -2729,7 +2726,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
         <v>33</v>
@@ -2746,7 +2743,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
         <v>34</v>
@@ -2766,7 +2763,7 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
         <v>35</v>
@@ -2786,7 +2783,7 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
         <v>36</v>
@@ -2806,7 +2803,7 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
         <v>37</v>
@@ -2815,10 +2812,13 @@
         <v>103</v>
       </c>
       <c r="E17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F17" t="s">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="G17" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2826,7 +2826,7 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
         <v>38</v>
@@ -5374,7 +5374,7 @@
         <v>14</v>
       </c>
       <c r="C97" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D97" t="s">
         <v>27</v>
@@ -5394,7 +5394,7 @@
         <v>14</v>
       </c>
       <c r="C98" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D98" t="s">
         <v>28</v>
@@ -5417,7 +5417,7 @@
         <v>14</v>
       </c>
       <c r="C99" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D99" t="s">
         <v>29</v>
@@ -5440,7 +5440,7 @@
         <v>14</v>
       </c>
       <c r="C100" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D100" t="s">
         <v>30</v>
@@ -5463,7 +5463,7 @@
         <v>14</v>
       </c>
       <c r="C101" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D101" t="s">
         <v>31</v>
@@ -5472,13 +5472,10 @@
         <v>102</v>
       </c>
       <c r="F101" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G101" t="s">
-        <v>89</v>
-      </c>
-      <c r="H101" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -5489,7 +5486,7 @@
         <v>14</v>
       </c>
       <c r="C102" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D102" t="s">
         <v>32</v>
@@ -5512,7 +5509,7 @@
         <v>14</v>
       </c>
       <c r="C103" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D103" t="s">
         <v>33</v>
@@ -5532,7 +5529,7 @@
         <v>14</v>
       </c>
       <c r="C104" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D104" t="s">
         <v>34</v>
@@ -5555,7 +5552,7 @@
         <v>14</v>
       </c>
       <c r="C105" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D105" t="s">
         <v>35</v>
@@ -5578,7 +5575,7 @@
         <v>14</v>
       </c>
       <c r="C106" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D106" t="s">
         <v>36</v>
@@ -5601,7 +5598,7 @@
         <v>14</v>
       </c>
       <c r="C107" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D107" t="s">
         <v>37</v>
@@ -5610,10 +5607,13 @@
         <v>103</v>
       </c>
       <c r="F107" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G107" t="s">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="H107" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -5624,7 +5624,7 @@
         <v>14</v>
       </c>
       <c r="C108" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D108" t="s">
         <v>38</v>
